--- a/artfynd/A 57608-2022 artfynd.xlsx
+++ b/artfynd/A 57608-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57608-2022 artfynd.xlsx
+++ b/artfynd/A 57608-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65351780</v>
+        <v>65351765</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597808.9200852317</v>
+        <v>597335</v>
       </c>
       <c r="R2" t="n">
-        <v>6823341.78750988</v>
+        <v>6823286</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,15 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>skiktad, äldre granskog med inslag av gamla granar</t>
+          <t>äldre barrblandskog</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>10 substratenheter # äldre granar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65351767</v>
+        <v>65351822</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597441.0718566766</v>
+        <v>597338</v>
       </c>
       <c r="R3" t="n">
-        <v>6823318.05967632</v>
+        <v>6823333</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,21 +853,11 @@
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -899,7 +869,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>lövrik, bördig äldre barrblandskog</t>
+          <t>kant av olikåldrig, asprik barrblandskog</t>
         </is>
       </c>
       <c r="AN3" t="n">
@@ -907,7 +877,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov asp</t>
+          <t>1 substratenheter # rikligt på gammal grov asp</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,37 +895,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65351821</v>
+        <v>65351763</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597592.9796397544</v>
+        <v>597375</v>
       </c>
       <c r="R4" t="n">
-        <v>6823456.915088123</v>
+        <v>6823321</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,21 +963,11 @@
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1024,7 +979,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>äldre granskog med viss skiktning, örtstråk</t>
+          <t>olikåldrig barrblandskog med inslag av gamla träd</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1042,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>65351761</v>
+        <v>65351779</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1082,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597375.1150490821</v>
+        <v>597809</v>
       </c>
       <c r="R5" t="n">
-        <v>6823300.933554878</v>
+        <v>6823342</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1115,21 +1073,11 @@
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1141,15 +1089,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>olikåldrig barrskog med inslag av gamla  träd</t>
+          <t>äldre, skiktad granskog med block och inslag av gammal gran</t>
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>10 substratenheter # gamla granar</t>
+          <t>1 substratenheter # granlåga av gammal gran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1167,15 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>65351779</v>
+        <v>65351781</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597808.9200852317</v>
+        <v>597795</v>
       </c>
       <c r="R6" t="n">
-        <v>6823341.78750988</v>
+        <v>6823362</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1240,21 +1183,11 @@
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1266,7 +1199,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>äldre, skiktad granskog med block och inslag av gammal gran</t>
+          <t>naturskogsartad barrskog</t>
         </is>
       </c>
       <c r="AN6" t="n">
@@ -1274,7 +1207,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga av gammal gran</t>
+          <t>1 substratenheter # förrötad granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1292,53 +1225,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>65351781</v>
+        <v>105314427</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Enångersån, S om, mellan Hästberget och kraftledning, Hls</t>
+          <t>Enångersån, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597794.9687184019</v>
+        <v>597335</v>
       </c>
       <c r="R7" t="n">
-        <v>6823361.915009957</v>
+        <v>6823788</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,22 +1290,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-03-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-03-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,65 +1307,52 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>naturskogsartad barrskog</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter # förrötad granlåga</t>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>65351769</v>
+        <v>65351760</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1457,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>597441.8288281632</v>
+        <v>597336</v>
       </c>
       <c r="R8" t="n">
-        <v>6823359.123509172</v>
+        <v>6823247</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1490,21 +1395,11 @@
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1516,15 +1411,15 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>lövrik, bördig, äldre barrblandskog</t>
+          <t>luckig, äldre barrblandskog</t>
         </is>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>7 substratenheter # grova aspar</t>
+          <t>5 substratenheter # äldre granar</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1542,37 +1437,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>65351763</v>
+        <v>65351761</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1582,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597375.0297432946</v>
+        <v>597375</v>
       </c>
       <c r="R9" t="n">
-        <v>6823320.97532447</v>
+        <v>6823301</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1615,21 +1505,11 @@
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1641,15 +1521,15 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>olikåldrig barrblandskog med inslag av gamla träd</t>
+          <t>olikåldrig barrskog med inslag av gamla  träd</t>
         </is>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga</t>
+          <t>10 substratenheter # gamla granar</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1667,15 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>65351822</v>
+        <v>105310940</v>
       </c>
       <c r="B10" t="n">
-        <v>78479</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,37 +1558,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>392</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Enångersån, S om, mellan Hästberget och kraftledning, Hls</t>
+          <t>Enångersån, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597337.8932515796</v>
+        <v>597346</v>
       </c>
       <c r="R10" t="n">
-        <v>6823332.817260335</v>
+        <v>6823805</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1737,22 +1612,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2017-03-24</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2017-03-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,43 +1629,35 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>kant av olikåldrig, asprik barrblandskog</t>
-        </is>
-      </c>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>1 substratenheter # rikligt på gammal grov asp</t>
+          <t>Rikligt i hela beståndet.</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>65351760</v>
+        <v>105310939</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,37 +1665,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Enångersån, S om, mellan Hästberget och kraftledning, Hls</t>
+          <t>Enångersån, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>597336.0063506789</v>
+        <v>597380</v>
       </c>
       <c r="R11" t="n">
-        <v>6823246.860216191</v>
+        <v>6823770</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1862,22 +1719,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-03-24</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-03-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,43 +1736,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>luckig, äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AN11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>5 substratenheter # äldre granar</t>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>65351765</v>
+        <v>65351773</v>
       </c>
       <c r="B12" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1933,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1957,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597334.9078039499</v>
+        <v>597698</v>
       </c>
       <c r="R12" t="n">
-        <v>6823285.963676259</v>
+        <v>6823301</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1990,21 +1824,11 @@
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2016,15 +1840,15 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>äldre barrblandskog</t>
+          <t>gammal luckig barrnaturskog på blockrik mark</t>
         </is>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>10 substratenheter # äldre granar</t>
+          <t>1 substratenheter # hård torraka, 28 cm bred</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2042,37 +1866,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>65351775</v>
+        <v>65351777</v>
       </c>
       <c r="B13" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2082,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597660.0923932524</v>
+        <v>597662</v>
       </c>
       <c r="R13" t="n">
-        <v>6823314.204304425</v>
+        <v>6823281</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2115,21 +1934,11 @@
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2017-03-24</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2141,15 +1950,15 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>äldre högrest granskog</t>
+          <t>gammal barrnaturskog på blockrik mark</t>
         </is>
       </c>
       <c r="AN13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>2 substratenheter # grova aspar</t>
+          <t>5 substratenheter # gamla granar</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2167,37 +1976,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105314427</v>
+        <v>105310938</v>
       </c>
       <c r="B14" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1205</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2207,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597334.6767899203</v>
+        <v>597379</v>
       </c>
       <c r="R14" t="n">
-        <v>6823787.505707432</v>
+        <v>6823771</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2240,19 +2044,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2284,53 +2078,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105310135</v>
+        <v>65351767</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Enångersån, Hls</t>
+          <t>Enångersån, S om, mellan Hästberget och kraftledning, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>597353.1981236319</v>
+        <v>597441</v>
       </c>
       <c r="R15" t="n">
-        <v>6823774.665212719</v>
+        <v>6823318</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2354,22 +2143,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2381,35 +2160,38 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>lövrik, bördig äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>105310939</v>
+        <v>65351769</v>
       </c>
       <c r="B16" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,37 +2199,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6426</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Enångersån, Hls</t>
+          <t>Enångersån, S om, mellan Hästberget och kraftledning, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597380.100740873</v>
+        <v>597442</v>
       </c>
       <c r="R16" t="n">
-        <v>6823769.695236638</v>
+        <v>6823359</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2471,22 +2253,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2498,35 +2270,38 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>lövrik, bördig, äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>7 substratenheter # grova aspar</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105310938</v>
+        <v>65351780</v>
       </c>
       <c r="B17" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2534,37 +2309,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Enångersån, Hls</t>
+          <t>Enångersån, S om, mellan Hästberget och kraftledning, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597379.1188690141</v>
+        <v>597809</v>
       </c>
       <c r="R17" t="n">
-        <v>6823770.621993233</v>
+        <v>6823342</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2588,22 +2363,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2615,35 +2380,38 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>skiktad, äldre granskog med inslag av gamla granar</t>
+        </is>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov asp</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105310940</v>
+        <v>65351772</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2651,37 +2419,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Enångersån, Hls</t>
+          <t>Enångersån, S om, mellan Hästberget och kraftledning, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597345.6685440572</v>
+        <v>597695</v>
       </c>
       <c r="R18" t="n">
-        <v>6823804.515713543</v>
+        <v>6823296</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2705,22 +2473,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2732,28 +2490,470 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>gammal luckig barrnaturskog på blockrik mark</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Rikligt i hela beståndet.</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
+          <t>1 substratenheter # hård torraka, 28 cm bred</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123419283</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>S Enångersån, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>597894</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6823283</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2024_2364</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Stuart Fell, Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>105310135</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Enångersån, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>597353</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6823775</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>65351821</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Enångersån, S om, mellan Hästberget och kraftledning, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>597593</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6823457</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2017-03-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2017-03-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>äldre granskog med viss skiktning, örtstråk</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>65351775</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Enångersån, S om, mellan Hästberget och kraftledning, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>597660</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6823314</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2017-03-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2017-03-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>äldre högrest granskog</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>2 substratenheter # grova aspar</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
